--- a/ImportTemplate/ภูมิปัญญา/expert-example-01.xlsx
+++ b/ImportTemplate/ภูมิปัญญา/expert-example-01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\biog\biog\ImportTemplate\ภูมิปัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B51C59-1822-4238-A77E-9468750034E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F82B10-14EB-41B8-923A-22487BAF59D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5989159A-E7FB-42B4-9C9A-65CB7C17A329}"/>
   </bookViews>
@@ -37,9 +37,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="86">
   <si>
-    <t>Template Import เนื้อหา ประเภทพืช</t>
-  </si>
-  <si>
     <t>พิกัด</t>
   </si>
   <si>
@@ -293,6 +290,9 @@
   </si>
   <si>
     <t>expert_01_cover.jpg</t>
+  </si>
+  <si>
+    <t>Template Import เนื้อหา ภูมิปัญญา</t>
   </si>
 </sst>
 </file>
@@ -995,7 +995,7 @@
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="11" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1023,206 +1023,206 @@
     </row>
     <row r="2" spans="1:26" ht="33.75" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="30.75" thickBot="1">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" t="s">
         <v>62</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" t="s">
         <v>64</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" t="s">
         <v>66</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>67</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>68</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>69</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>70</v>
-      </c>
-      <c r="R3" t="s">
-        <v>71</v>
       </c>
       <c r="S3">
         <v>10330</v>
       </c>
       <c r="T3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="45">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
         <v>73</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>75</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>76</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>77</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>78</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>79</v>
       </c>
-      <c r="N4" t="s">
-        <v>80</v>
-      </c>
       <c r="O4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" t="s">
         <v>68</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>70</v>
-      </c>
-      <c r="R4" t="s">
-        <v>71</v>
       </c>
       <c r="S4">
         <v>10330</v>
       </c>
       <c r="T4" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" t="s">
+        <v>83</v>
+      </c>
+      <c r="V4" t="s">
         <v>81</v>
       </c>
-      <c r="U4" t="s">
-        <v>84</v>
-      </c>
-      <c r="V4" t="s">
-        <v>82</v>
-      </c>
       <c r="X4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="2:2">
@@ -1297,42 +1297,42 @@
   <sheetData>
     <row r="4" spans="2:11">
       <c r="B4" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="12"/>
       <c r="E4" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="12"/>
       <c r="H4" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="12"/>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="15.75" thickBot="1">
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
       <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -1340,22 +1340,22 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="15.75" thickBot="1">
@@ -1363,77 +1363,77 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="15.75" thickBot="1">
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="45">
       <c r="H9" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="2:11">
       <c r="H10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:11">
       <c r="H11" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:11">
       <c r="H12" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
